--- a/data/import/lintec.xlsx
+++ b/data/import/lintec.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U129"/>
+  <dimension ref="A1:V129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,6 +522,11 @@
           <t>pub</t>
         </is>
       </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>tds</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -600,6 +605,11 @@
       <c r="U2" t="n">
         <v>0</v>
       </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/labelstocks/highlight/bubble_free/</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -678,6 +688,11 @@
       <c r="U3" t="n">
         <v>0</v>
       </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/labelstocks/highlight/bubble_free/</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -743,6 +758,11 @@
       <c r="U4" t="n">
         <v>0</v>
       </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/labelstocks/highlight/lock_tight/</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -808,6 +828,11 @@
       <c r="U5" t="n">
         <v>0</v>
       </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/labelstocks/highlight/oil_tol/</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -873,6 +898,11 @@
       <c r="U6" t="n">
         <v>0</v>
       </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/labelstocks/highlight/oil_tol/</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -943,6 +973,11 @@
       <c r="U7" t="n">
         <v>0</v>
       </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/labelstocks/highlight/cryogenic/</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1013,6 +1048,11 @@
       <c r="U8" t="n">
         <v>0</v>
       </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/labelstocks/highlight/cryogenic/</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1086,6 +1126,11 @@
       <c r="U9" t="n">
         <v>0</v>
       </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/labelstocks/highlight/eye_catching/high.html</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1159,6 +1204,11 @@
       <c r="U10" t="n">
         <v>0</v>
       </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/labelstocks/highlight/eye_catching/high.html</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1232,6 +1282,11 @@
       <c r="U11" t="n">
         <v>0</v>
       </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/labelstocks/highlight/eye_catching/high.html</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1305,6 +1360,11 @@
       <c r="U12" t="n">
         <v>0</v>
       </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/labelstocks/highlight/eye_catching/low.html</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1378,6 +1438,11 @@
       <c r="U13" t="n">
         <v>0</v>
       </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/labelstocks/highlight/eye_catching/low.html</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1438,6 +1503,11 @@
       <c r="U14" t="n">
         <v>0</v>
       </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/labelstocks/highlight/environmentally/kee_kep.html</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1498,6 +1568,11 @@
       <c r="U15" t="n">
         <v>0</v>
       </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/labelstocks/highlight/environmentally/kee_kep.html</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1558,6 +1633,11 @@
       <c r="U16" t="n">
         <v>0</v>
       </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/labelstocks/highlight/environmentally/kee_kep.html</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1618,6 +1698,11 @@
       <c r="U17" t="n">
         <v>0</v>
       </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/labelstocks/highlight/environmentally/kee_kep.html</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1688,6 +1773,11 @@
       <c r="U18" t="n">
         <v>0</v>
       </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/labelstocks/highlight/environmentally/kes_kea.html</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1758,6 +1848,11 @@
       <c r="U19" t="n">
         <v>0</v>
       </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/labelstocks/highlight/environmentally/kes_kea.html</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1828,6 +1923,11 @@
       <c r="U20" t="n">
         <v>0</v>
       </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/labelstocks/highlight/environmentally/kes_kea.html</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1898,6 +1998,11 @@
       <c r="U21" t="n">
         <v>0</v>
       </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/labelstocks/highlight/environmentally/kes_kea.html</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1963,6 +2068,11 @@
       <c r="U22" t="n">
         <v>0</v>
       </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/labelstocks/highlight/environmentally/kes_kea.html</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2033,6 +2143,11 @@
       <c r="U23" t="n">
         <v>0</v>
       </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/labelstocks/highlight/environmentally/kes_kea.html</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2098,6 +2213,11 @@
       <c r="U24" t="n">
         <v>0</v>
       </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/labelstocks/highlight/environmentally/kes_kea.html</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2163,6 +2283,11 @@
       <c r="U25" t="n">
         <v>0</v>
       </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/labelstocks/highlight/environmentally/kes_kea.html</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2228,6 +2353,11 @@
       <c r="U26" t="n">
         <v>0</v>
       </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/labelstocks/highlight/environmentally/kes_kea.html</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2301,6 +2431,11 @@
       <c r="U27" t="n">
         <v>0</v>
       </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/labelstocks/highlight/environmentally/kp.html</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2356,6 +2491,11 @@
       <c r="U28" t="n">
         <v>0</v>
       </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/topics/newsrelease/2025/250306_a.html</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2421,6 +2561,11 @@
       <c r="U29" t="n">
         <v>0</v>
       </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/variable/inkjet.html</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2486,6 +2631,11 @@
       <c r="U30" t="n">
         <v>0</v>
       </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/variable/inkjet.html</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2551,6 +2701,11 @@
       <c r="U31" t="n">
         <v>0</v>
       </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/variable/inkjet.html</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2616,6 +2771,11 @@
       <c r="U32" t="n">
         <v>0</v>
       </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/variable/inkjet.html</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2686,6 +2846,11 @@
       <c r="U33" t="n">
         <v>0</v>
       </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/variable/electro.html</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2756,6 +2921,11 @@
       <c r="U34" t="n">
         <v>0</v>
       </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/variable/electro.html</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2826,6 +2996,11 @@
       <c r="U35" t="n">
         <v>0</v>
       </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/variable/electro.html</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2896,6 +3071,11 @@
       <c r="U36" t="n">
         <v>0</v>
       </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/variable/electro.html</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2966,6 +3146,11 @@
       <c r="U37" t="n">
         <v>0</v>
       </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/variable/electro.html</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3036,6 +3221,11 @@
       <c r="U38" t="n">
         <v>0</v>
       </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/variable/electro.html</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3106,6 +3296,11 @@
       <c r="U39" t="n">
         <v>0</v>
       </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/variable/electro.html</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3176,6 +3371,11 @@
       <c r="U40" t="n">
         <v>0</v>
       </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/variable/electro.html</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3246,6 +3446,11 @@
       <c r="U41" t="n">
         <v>0</v>
       </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/variable/electro.html</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3316,6 +3521,11 @@
       <c r="U42" t="n">
         <v>0</v>
       </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/variable/electro.html</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3381,6 +3591,11 @@
       <c r="U43" t="n">
         <v>0</v>
       </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/variable/thermal_transfer.html</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3446,6 +3661,11 @@
       <c r="U44" t="n">
         <v>0</v>
       </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/variable/thermal_transfer.html</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3511,6 +3731,11 @@
       <c r="U45" t="n">
         <v>0</v>
       </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/variable/thermal_transfer.html</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3576,6 +3801,11 @@
       <c r="U46" t="n">
         <v>0</v>
       </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/variable/thermal_transfer.html</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3641,6 +3871,11 @@
       <c r="U47" t="n">
         <v>0</v>
       </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/variable/thermal_transfer.html</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3706,6 +3941,11 @@
       <c r="U48" t="n">
         <v>0</v>
       </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/variable/thermal_transfer.html</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3776,6 +4016,11 @@
       <c r="U49" t="n">
         <v>0</v>
       </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/variable/thermal_transfer.html</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3846,6 +4091,11 @@
       <c r="U50" t="n">
         <v>0</v>
       </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/variable/thermal_transfer.html</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3916,6 +4166,11 @@
       <c r="U51" t="n">
         <v>0</v>
       </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/variable/thermal_transfer.html</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3986,6 +4241,11 @@
       <c r="U52" t="n">
         <v>0</v>
       </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/variable/thermal_transfer.html</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4051,6 +4311,11 @@
       <c r="U53" t="n">
         <v>0</v>
       </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/variable/thermal_transfer.html</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4121,6 +4386,11 @@
       <c r="U54" t="n">
         <v>0</v>
       </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/variable/thermal_transfer.html</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4191,6 +4461,11 @@
       <c r="U55" t="n">
         <v>0</v>
       </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/variable/thermal_transfer.html</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4261,6 +4536,11 @@
       <c r="U56" t="n">
         <v>0</v>
       </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/variable/thermal_transfer.html</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4331,6 +4611,11 @@
       <c r="U57" t="n">
         <v>0</v>
       </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/variable/thermal_transfer.html</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4401,6 +4686,11 @@
       <c r="U58" t="n">
         <v>0</v>
       </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/variable/thermal_transfer.html</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4471,6 +4761,11 @@
       <c r="U59" t="n">
         <v>0</v>
       </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/variable/thermal_transfer.html</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4536,6 +4831,11 @@
       <c r="U60" t="n">
         <v>0</v>
       </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/variable/thermal_transfer.html</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4606,6 +4906,11 @@
       <c r="U61" t="n">
         <v>0</v>
       </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/variable/thermal_transfer.html</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4676,6 +4981,11 @@
       <c r="U62" t="n">
         <v>0</v>
       </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/variable/thermal_transfer.html</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4746,6 +5056,11 @@
       <c r="U63" t="n">
         <v>0</v>
       </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/variable/thermal_transfer.html</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4817,6 +5132,11 @@
       <c r="U64" t="n">
         <v>1</v>
       </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/variable/thermal_transfer.html</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4883,6 +5203,11 @@
       <c r="U65" t="n">
         <v>0</v>
       </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/variable/thermal_transfer.html</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4954,6 +5279,11 @@
       <c r="U66" t="n">
         <v>1</v>
       </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/variable/thermal_transfer.html</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5025,6 +5355,11 @@
       <c r="U67" t="n">
         <v>1</v>
       </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/variable/thermal_transfer.html</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -5090,6 +5425,11 @@
       <c r="U68" t="n">
         <v>0</v>
       </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/variable/direct_thermal.html</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5155,6 +5495,11 @@
       <c r="U69" t="n">
         <v>0</v>
       </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/variable/direct_thermal.html</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -5220,6 +5565,11 @@
       <c r="U70" t="n">
         <v>0</v>
       </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/variable/direct_thermal.html</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5285,6 +5635,11 @@
       <c r="U71" t="n">
         <v>0</v>
       </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/variable/direct_thermal.html</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5350,6 +5705,11 @@
       <c r="U72" t="n">
         <v>0</v>
       </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/variable/direct_thermal.html</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5415,6 +5775,11 @@
       <c r="U73" t="n">
         <v>0</v>
       </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/variable/direct_thermal.html</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5480,6 +5845,11 @@
       <c r="U74" t="n">
         <v>0</v>
       </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/variable/direct_thermal.html</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5545,6 +5915,11 @@
       <c r="U75" t="n">
         <v>0</v>
       </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/variable/direct_thermal.html</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5610,6 +5985,11 @@
       <c r="U76" t="n">
         <v>0</v>
       </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/variable/direct_thermal.html</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5675,6 +6055,11 @@
       <c r="U77" t="n">
         <v>0</v>
       </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/variable/direct_thermal.html</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5740,6 +6125,11 @@
       <c r="U78" t="n">
         <v>0</v>
       </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/variable/direct_thermal.html</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5805,6 +6195,11 @@
       <c r="U79" t="n">
         <v>0</v>
       </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/variable/direct_thermal.html</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5873,6 +6268,11 @@
       <c r="U80" t="n">
         <v>0</v>
       </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/ul_cul/</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5941,6 +6341,11 @@
       <c r="U81" t="n">
         <v>0</v>
       </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/ul_cul/</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -6009,6 +6414,11 @@
       <c r="U82" t="n">
         <v>0</v>
       </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/ul_cul/</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -6077,6 +6487,11 @@
       <c r="U83" t="n">
         <v>0</v>
       </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/ul_cul/</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -6145,6 +6560,11 @@
       <c r="U84" t="n">
         <v>0</v>
       </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/ul_cul/</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -6213,6 +6633,11 @@
       <c r="U85" t="n">
         <v>0</v>
       </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/ul_cul/</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -6281,6 +6706,11 @@
       <c r="U86" t="n">
         <v>0</v>
       </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/ul_cul/</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -6349,6 +6779,11 @@
       <c r="U87" t="n">
         <v>0</v>
       </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/ul_cul/</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -6417,6 +6852,11 @@
       <c r="U88" t="n">
         <v>0</v>
       </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/ul_cul/</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -6485,6 +6925,11 @@
       <c r="U89" t="n">
         <v>0</v>
       </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/label/ul_cul/</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -6545,6 +6990,11 @@
       <c r="U90" t="n">
         <v>0</v>
       </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/industry/industrial_use_adhesive_tapes/pdf/TL-201.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -6605,6 +7055,11 @@
       <c r="U91" t="n">
         <v>0</v>
       </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/industry/industrial_use_adhesive_tapes/pdf/TL-202.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -6665,6 +7120,11 @@
       <c r="U92" t="n">
         <v>0</v>
       </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/industry/industrial_use_adhesive_tapes/pdf/TL-205.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -6725,6 +7185,11 @@
       <c r="U93" t="n">
         <v>0</v>
       </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/industry/industrial_use_adhesive_tapes/pdf/TL-250.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -6785,6 +7250,11 @@
       <c r="U94" t="n">
         <v>0</v>
       </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/industry/industrial_use_adhesive_tapes/pdf/TL-13K.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -6845,6 +7315,11 @@
       <c r="U95" t="n">
         <v>0</v>
       </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/industry/industrial_use_adhesive_tapes/pdf/TL-202S.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -6905,6 +7380,11 @@
       <c r="U96" t="n">
         <v>0</v>
       </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/industry/industrial_use_adhesive_tapes/pdf/TL-250S.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6960,6 +7440,11 @@
       <c r="U97" t="n">
         <v>0</v>
       </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/industry/industrial_use_adhesive_tapes/pdf/TL-701.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -7015,6 +7500,11 @@
       <c r="U98" t="n">
         <v>0</v>
       </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/industry/industrial_use_adhesive_tapes/pdf/TL-70.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -7070,6 +7560,11 @@
       <c r="U99" t="n">
         <v>0</v>
       </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/industry/industrial_use_adhesive_tapes/pdf/TL-71.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -7125,6 +7620,11 @@
       <c r="U100" t="n">
         <v>0</v>
       </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/industry/industrial_use_adhesive_tapes/pdf/TL-75K.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -7180,6 +7680,11 @@
       <c r="U101" t="n">
         <v>0</v>
       </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/industry/industrial_use_adhesive_tapes/pdf/TL-83.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -7235,6 +7740,11 @@
       <c r="U102" t="n">
         <v>0</v>
       </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/industry/industrial_use_adhesive_tapes/pdf/TL-83S-AR.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -7295,6 +7805,11 @@
       <c r="U103" t="n">
         <v>0</v>
       </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/industry/industrial_use_adhesive_tapes/pdf/TL-52BM-05.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -7355,6 +7870,11 @@
       <c r="U104" t="n">
         <v>0</v>
       </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/industry/industrial_use_adhesive_tapes/pdf/TL-52BM-08.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -7415,6 +7935,11 @@
       <c r="U105" t="n">
         <v>0</v>
       </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/industry/industrial_use_adhesive_tapes/pdf/TL-52BM-12.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -7475,6 +8000,11 @@
       <c r="U106" t="n">
         <v>0</v>
       </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/industry/industrial_use_adhesive_tapes/pdf/TL-52BU-08.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -7535,6 +8065,11 @@
       <c r="U107" t="n">
         <v>0</v>
       </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/industry/industrial_use_adhesive_tapes/pdf/TL-52WU-10.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -7595,6 +8130,11 @@
       <c r="U108" t="n">
         <v>0</v>
       </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/industry/industrial_use_adhesive_tapes/pdf/TL-54-06.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -7650,6 +8190,11 @@
       <c r="U109" t="n">
         <v>0</v>
       </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/industry/industrial_use_adhesive_tapes/pdf/TL-430S-06.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -7705,6 +8250,11 @@
       <c r="U110" t="n">
         <v>0</v>
       </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/industry/industrial_use_adhesive_tapes/pdf/TL-450S-16.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -7760,6 +8310,11 @@
       <c r="U111" t="n">
         <v>0</v>
       </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/industry/industrial_use_adhesive_tapes/pdf/TL-4100S-50.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -7815,6 +8370,11 @@
       <c r="U112" t="n">
         <v>0</v>
       </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/industry/industrial_use_adhesive_tapes/pdf/PT25NB.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -7870,6 +8430,11 @@
       <c r="U113" t="n">
         <v>0</v>
       </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/industry/industrial_use_adhesive_tapes/pdf/PT50NB.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -7925,6 +8490,11 @@
       <c r="U114" t="n">
         <v>0</v>
       </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/industry/industrial_use_adhesive_tapes/pdf/PT100NB.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -7980,6 +8550,11 @@
       <c r="U115" t="n">
         <v>0</v>
       </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/industry/industrial_use_adhesive_tapes/pdf/SRL-0759(AS).pdf</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -8035,6 +8610,11 @@
       <c r="U116" t="n">
         <v>0</v>
       </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/industry/industrial_use_adhesive_tapes/pdf/SRL-0758(AS).pdf</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -8090,6 +8670,11 @@
       <c r="U117" t="n">
         <v>0</v>
       </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/industry/industrial_use_adhesive_tapes/pdf/SRL-0754(AS).pdf</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -8145,6 +8730,11 @@
       <c r="U118" t="n">
         <v>0</v>
       </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/industry/industrial_use_adhesive_tapes/pdf/SRL-0753(AS).pdf</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -8200,6 +8790,11 @@
       <c r="U119" t="n">
         <v>0</v>
       </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/industry/industrial_use_adhesive_tapes/pdf/SRL-0753B(AS).pdf</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -8255,6 +8850,11 @@
       <c r="U120" t="n">
         <v>0</v>
       </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/industry/industrial_use_adhesive_tapes/pdf/SRL-0753C(AS).pdf</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -8310,6 +8910,11 @@
       <c r="U121" t="n">
         <v>0</v>
       </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/industry/industrial_use_adhesive_tapes/pdf/SRL-0504.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -8365,6 +8970,11 @@
       <c r="U122" t="n">
         <v>0</v>
       </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/industry/industrial_use_adhesive_tapes/pdf/SRL-0758Red.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -8420,6 +9030,11 @@
       <c r="U123" t="n">
         <v>0</v>
       </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/industry/industrial_use_adhesive_tapes/pdf/SRL-1258.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -8475,6 +9090,11 @@
       <c r="U124" t="n">
         <v>0</v>
       </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/industry/industrial_use_adhesive_tapes/pdf/SRL-1254.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -8530,6 +9150,11 @@
       <c r="U125" t="n">
         <v>0</v>
       </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/industry/industrial_use_adhesive_tapes/pdf/SRL-125F.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -8585,6 +9210,11 @@
       <c r="U126" t="n">
         <v>0</v>
       </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/industry/industrial_use_adhesive_tapes/pdf/SRL-050F(SF).pdf</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -8640,6 +9270,11 @@
       <c r="U127" t="n">
         <v>0</v>
       </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/industry/industrial_use_adhesive_tapes/pdf/SRL-050F(SFCL).pdf</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -8695,6 +9330,11 @@
       <c r="U128" t="n">
         <v>0</v>
       </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/industry/industrial_use_adhesive_tapes/pdf/CLEAR-PET50-06-50.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -8749,6 +9389,11 @@
       </c>
       <c r="U129" t="n">
         <v>0</v>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>https://www.lintec-global.com/products/industry/industrial_use_adhesive_tapes/</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/import/lintec.xlsx
+++ b/data/import/lintec.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V129"/>
+  <dimension ref="A1:W129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -527,6 +527,11 @@
           <t>tds</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>sub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
